--- a/老余裸K圖表_20260617/老余裸K_賺賠比精選_20260617.xlsx
+++ b/老余裸K圖表_20260617/老余裸K_賺賠比精選_20260617.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -547,33 +547,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2630.TW</t>
+          <t>6425.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>易發</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1 : 12.95</t>
+          <t>1 : 8.0</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>39.2</v>
+        <v>77.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>38.15</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>52.8</v>
+        <v>109</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>931</v>
+        <v>567</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -584,33 +584,33 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>6425.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>易發</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>1 : 8.0</t>
+          <t>1 : 4.82</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>77.8</v>
+        <v>2245</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>73.90000000000001</v>
+        <v>2025</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>109</v>
+        <v>3305</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>3.9</v>
+        <v>220</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>567</v>
+        <v>2124</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,33 +621,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3563.TW</t>
+          <t>6199.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>天品</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1 : 7.56</t>
+          <t>1 : 4.67</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>702</v>
+        <v>92.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>663</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>997</v>
+        <v>116</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>39</v>
+        <v>5.1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>588</v>
+        <v>1069</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -658,33 +658,33 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>4956.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1 : 7.29</t>
+          <t>1 : 3.85</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>38.6</v>
+        <v>903</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>35.65</v>
+        <v>796</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>60.1</v>
+        <v>1315</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2.95</v>
+        <v>107</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1258</v>
+        <v>4313</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -695,33 +695,33 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3437.TW</t>
+          <t>6233.TWO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>榮創</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1 : 6.35</t>
+          <t>1 : 3.65</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>21.45</v>
+        <v>24.15</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>19.9</v>
+        <v>22.3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>938</v>
+        <v>599</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -732,33 +732,33 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2449.TW</t>
+          <t>1815.TWO</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.94</t>
+          <t>1 : 3.45</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>280.5</v>
+        <v>95</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>263.5</v>
+        <v>85</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>364.5</v>
+        <v>129.5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8673</v>
+        <v>10297</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -769,33 +769,33 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>5443.TWO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.82</t>
+          <t>1 : 3.34</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2245</v>
+        <v>104.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2025</v>
+        <v>94.16</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3305</v>
+        <v>139</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>220</v>
+        <v>10.34</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2124</v>
+        <v>796</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -806,33 +806,33 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>1711.TW</t>
+          <t>3466.TWO</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>德晉</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.78</t>
+          <t>1 : 3.27</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>44.45</v>
+        <v>33.85</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>40.3</v>
+        <v>30.2</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>64.3</v>
+        <v>45.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>5305</v>
+        <v>996</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -843,33 +843,33 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6199.TWO</t>
+          <t>3689.TWO</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>天品</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.67</t>
+          <t>1 : 3.12</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>92.2</v>
+        <v>118.5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>110</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1069</v>
+        <v>866</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -880,33 +880,33 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>3031.TW</t>
+          <t>3289.TWO</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>宜特</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.52</t>
+          <t>1 : 2.41</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>28.3</v>
+        <v>169.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>26.75</v>
+        <v>149</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>35.3</v>
+        <v>219</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>1.55</v>
+        <v>20.5</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>765</v>
+        <v>2784</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -917,627 +917,35 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3645.TW</t>
+          <t>4979.TWO</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.08</t>
+          <t>1 : 2.35</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>92.5</v>
+        <v>546</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>454</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>121.5</v>
+        <v>762</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.1</v>
+        <v>92</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1268</v>
+        <v>6897</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>3062.TW</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>建漢</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.94</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>31.95</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>3095</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2419.TW</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>仲琦</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.85</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>29.65</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>27.35</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>1384</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>3163.TWO</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.85</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>903</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>796</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>1315</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>107</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>4313</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>1717.TW</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>長興</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.69</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>6787</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>6233.TWO</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>旺玖</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.65</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>599</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1815.TWO</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>富喬</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.45</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>129.5</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>10297</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>3714.TW</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>富采</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.42</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>9871</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5443.TWO</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.34</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>94.16</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>796</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>1519.TW</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.29</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>803</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>744</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>997</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>3938</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3466.TWO</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>德晉</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.27</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>996</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>3689.TWO</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>湧德</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>1 : 3.12</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>866</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6438.TW</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>迅得</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>1 : 3.06</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>138.12</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>190.41</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>733</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>3030.TW</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>1 : 2.91</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>293</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>447.59</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>1133</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3533.TW</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>1 : 2.52</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>2300</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>2955</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1449</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>3289.TWO</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>宜特</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>1 : 2.41</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>149</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>219</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>4979.TWO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>1 : 2.35</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>546</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>454</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>762</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>6897</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1556,22 +964,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
